--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127118668</v>
       </c>
       <c r="B3" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127117885</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127117979</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127118450</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127117773</v>
+        <v>127117753</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,32 +1379,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127117753</v>
+        <v>127117773</v>
       </c>
       <c r="B9" t="n">
-        <v>80112</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
         <v>127119304</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>91319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,39 +1691,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R12" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,7 +1780,7 @@
         <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127119084</v>
+        <v>127118286</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,34 +1885,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594836</v>
+        <v>594818</v>
       </c>
       <c r="R14" t="n">
-        <v>6985204</v>
+        <v>6985155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1984,7 +1984,7 @@
         <v>127119155</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127120162</v>
+        <v>127119947</v>
       </c>
       <c r="B19" t="n">
         <v>57657</v>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594780</v>
+        <v>594720</v>
       </c>
       <c r="R19" t="n">
-        <v>6985201</v>
+        <v>6985260</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,7 +2506,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127119947</v>
+        <v>127120162</v>
       </c>
       <c r="B20" t="n">
         <v>57657</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594720</v>
+        <v>594780</v>
       </c>
       <c r="R20" t="n">
-        <v>6985260</v>
+        <v>6985201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
         <v>127118859</v>
       </c>
       <c r="B21" t="n">
-        <v>96487</v>
+        <v>96562</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127119033</v>
       </c>
       <c r="B23" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>127118617</v>
       </c>
       <c r="B24" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B3" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R3" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R4" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
         <v>127117979</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127120021</v>
+        <v>127118450</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,39 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594741</v>
+        <v>594888</v>
       </c>
       <c r="R6" t="n">
-        <v>6985230</v>
+        <v>6985235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127118450</v>
+        <v>127120021</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1186,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594888</v>
+        <v>594741</v>
       </c>
       <c r="R7" t="n">
-        <v>6985235</v>
+        <v>6985230</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1251,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,7 +1285,7 @@
         <v>127117753</v>
       </c>
       <c r="B8" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127117773</v>
       </c>
       <c r="B9" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127119304</v>
       </c>
       <c r="B10" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127119084</v>
       </c>
       <c r="B12" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>127119155</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>127118859</v>
       </c>
       <c r="B21" t="n">
-        <v>96562</v>
+        <v>96568</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127119033</v>
       </c>
       <c r="B23" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>127118617</v>
       </c>
       <c r="B24" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -1777,45 +1777,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R13" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,50 +1884,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127118286</v>
+        <v>127119169</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594818</v>
+        <v>594800</v>
       </c>
       <c r="R14" t="n">
-        <v>6985155</v>
+        <v>6985218</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1955,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R3" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B4" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R4" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B12" t="n">
-        <v>91325</v>
+        <v>80145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R12" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,39 +1788,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R13" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1848,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,45 +1874,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B14" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R14" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R3" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R4" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
         <v>127119084</v>
       </c>
       <c r="B13" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>127118859</v>
       </c>
       <c r="B21" t="n">
-        <v>96568</v>
+        <v>96569</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127119304</v>
+        <v>127120216</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,34 +1487,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594796</v>
+        <v>594780</v>
       </c>
       <c r="R10" t="n">
-        <v>6985272</v>
+        <v>6985191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127120216</v>
+        <v>127119304</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,39 +1594,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594780</v>
+        <v>594796</v>
       </c>
       <c r="R11" t="n">
-        <v>6985191</v>
+        <v>6985272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,45 +1680,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B12" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R12" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,32 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R13" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,39 +1895,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R14" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1955,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127120216</v>
+        <v>127119304</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,39 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594780</v>
+        <v>594796</v>
       </c>
       <c r="R10" t="n">
-        <v>6985191</v>
+        <v>6985272</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127119304</v>
+        <v>127120216</v>
       </c>
       <c r="B11" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,34 +1584,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594796</v>
+        <v>594780</v>
       </c>
       <c r="R11" t="n">
-        <v>6985272</v>
+        <v>6985191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1649,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,50 +1680,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127118286</v>
+        <v>127119169</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594818</v>
+        <v>594800</v>
       </c>
       <c r="R12" t="n">
-        <v>6985155</v>
+        <v>6985218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119169</v>
+        <v>127119084</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>91326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594800</v>
+        <v>594836</v>
       </c>
       <c r="R13" t="n">
-        <v>6985218</v>
+        <v>6985204</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127119084</v>
+        <v>127118286</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,34 +1885,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594836</v>
+        <v>594818</v>
       </c>
       <c r="R14" t="n">
-        <v>6985204</v>
+        <v>6985155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R3" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B4" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R4" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1680,45 +1680,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B12" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R12" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,32 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R13" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,39 +1895,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R14" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1955,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127118187</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127118668</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127117885</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127117979</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127118450</v>
+        <v>127120021</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,34 +1089,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594888</v>
+        <v>594741</v>
       </c>
       <c r="R6" t="n">
-        <v>6985235</v>
+        <v>6985230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1154,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127120021</v>
+        <v>127118450</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,39 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594741</v>
+        <v>594888</v>
       </c>
       <c r="R7" t="n">
-        <v>6985230</v>
+        <v>6985235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,7 +1285,7 @@
         <v>127117753</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127117773</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127119304</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127120216</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>91330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,39 +1691,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R12" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,45 +1777,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R13" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,32 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R14" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1984,7 @@
         <v>127119155</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127119902</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127118223</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127118384</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>127119947</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127120162</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>127118859</v>
       </c>
       <c r="B21" t="n">
-        <v>96569</v>
+        <v>96573</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127118321</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127119033</v>
       </c>
       <c r="B23" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>127118617</v>
       </c>
       <c r="B24" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B3" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R3" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R4" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127120021</v>
+        <v>127118450</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,39 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594741</v>
+        <v>594888</v>
       </c>
       <c r="R6" t="n">
-        <v>6985230</v>
+        <v>6985235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127118450</v>
+        <v>127120021</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1186,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594888</v>
+        <v>594741</v>
       </c>
       <c r="R7" t="n">
-        <v>6985235</v>
+        <v>6985230</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1251,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B12" t="n">
-        <v>91330</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R12" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,39 +1788,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R13" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1848,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,45 +1874,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R14" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R3" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B4" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R4" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -1680,45 +1680,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R12" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,32 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>91330</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R13" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,39 +1895,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R14" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1955,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127118450</v>
+        <v>127120021</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,34 +1089,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594888</v>
+        <v>594741</v>
       </c>
       <c r="R6" t="n">
-        <v>6985235</v>
+        <v>6985230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1154,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127120021</v>
+        <v>127118450</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,39 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594741</v>
+        <v>594888</v>
       </c>
       <c r="R7" t="n">
-        <v>6985230</v>
+        <v>6985235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127119304</v>
+        <v>127120216</v>
       </c>
       <c r="B10" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,34 +1487,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594796</v>
+        <v>594780</v>
       </c>
       <c r="R10" t="n">
-        <v>6985272</v>
+        <v>6985191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127120216</v>
+        <v>127119304</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,39 +1594,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594780</v>
+        <v>594796</v>
       </c>
       <c r="R11" t="n">
-        <v>6985191</v>
+        <v>6985272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,50 +1680,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127118286</v>
+        <v>127119169</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594818</v>
+        <v>594800</v>
       </c>
       <c r="R12" t="n">
-        <v>6985155</v>
+        <v>6985218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119169</v>
+        <v>127119084</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>91330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594800</v>
+        <v>594836</v>
       </c>
       <c r="R13" t="n">
-        <v>6985218</v>
+        <v>6985204</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127119084</v>
+        <v>127118286</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,34 +1885,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594836</v>
+        <v>594818</v>
       </c>
       <c r="R14" t="n">
-        <v>6985204</v>
+        <v>6985155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127118187</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B3" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R3" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R4" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
         <v>127117979</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127120021</v>
+        <v>127118450</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,39 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594741</v>
+        <v>594888</v>
       </c>
       <c r="R6" t="n">
-        <v>6985230</v>
+        <v>6985235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127118450</v>
+        <v>127120021</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1186,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594888</v>
+        <v>594741</v>
       </c>
       <c r="R7" t="n">
-        <v>6985235</v>
+        <v>6985230</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1251,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,7 +1285,7 @@
         <v>127117753</v>
       </c>
       <c r="B8" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127117773</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127120216</v>
+        <v>127119304</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,39 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594780</v>
+        <v>594796</v>
       </c>
       <c r="R10" t="n">
-        <v>6985191</v>
+        <v>6985272</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127119304</v>
+        <v>127120216</v>
       </c>
       <c r="B11" t="n">
-        <v>80121</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,34 +1584,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594796</v>
+        <v>594780</v>
       </c>
       <c r="R11" t="n">
-        <v>6985272</v>
+        <v>6985191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1649,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119169</v>
+        <v>127119084</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>91332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594800</v>
+        <v>594836</v>
       </c>
       <c r="R12" t="n">
-        <v>6985218</v>
+        <v>6985204</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>91330</v>
+        <v>80151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R13" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
         <v>127118286</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>127119155</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127119902</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127118223</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127118384</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>127119947</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127120162</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>127118859</v>
       </c>
       <c r="B21" t="n">
-        <v>96573</v>
+        <v>96575</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127118321</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127119033</v>
       </c>
       <c r="B23" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>127118617</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>80151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R12" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119169</v>
+        <v>127119084</v>
       </c>
       <c r="B13" t="n">
-        <v>80151</v>
+        <v>91332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594800</v>
+        <v>594836</v>
       </c>
       <c r="R13" t="n">
-        <v>6985218</v>
+        <v>6985204</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127118450</v>
+        <v>127120021</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,34 +1089,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594888</v>
+        <v>594741</v>
       </c>
       <c r="R6" t="n">
-        <v>6985235</v>
+        <v>6985230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1154,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127120021</v>
+        <v>127118450</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,39 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594741</v>
+        <v>594888</v>
       </c>
       <c r="R7" t="n">
-        <v>6985230</v>
+        <v>6985235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119084</v>
+        <v>127118286</v>
       </c>
       <c r="B13" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,34 +1788,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594836</v>
+        <v>594818</v>
       </c>
       <c r="R13" t="n">
-        <v>6985204</v>
+        <v>6985155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,39 +1895,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R14" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1955,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R3" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B4" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R4" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127120021</v>
+        <v>127118450</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,39 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594741</v>
+        <v>594888</v>
       </c>
       <c r="R6" t="n">
-        <v>6985230</v>
+        <v>6985235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127118450</v>
+        <v>127120021</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1186,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594888</v>
+        <v>594741</v>
       </c>
       <c r="R7" t="n">
-        <v>6985235</v>
+        <v>6985230</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1251,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1680,45 +1680,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B12" t="n">
-        <v>80151</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R12" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,39 +1798,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R13" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,32 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>80151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R14" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127119947</v>
+        <v>127120162</v>
       </c>
       <c r="B19" t="n">
         <v>57663</v>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594720</v>
+        <v>594780</v>
       </c>
       <c r="R19" t="n">
-        <v>6985260</v>
+        <v>6985201</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,7 +2506,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127120162</v>
+        <v>127119947</v>
       </c>
       <c r="B20" t="n">
         <v>57663</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594780</v>
+        <v>594720</v>
       </c>
       <c r="R20" t="n">
-        <v>6985201</v>
+        <v>6985260</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
         <v>127118859</v>
       </c>
       <c r="B21" t="n">
-        <v>96575</v>
+        <v>96581</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127118187</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B3" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R3" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R4" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
         <v>127117979</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127118450</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127120021</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127117753</v>
       </c>
       <c r="B8" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127117773</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127119304</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127120216</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>91341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,39 +1691,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R12" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>91338</v>
+        <v>80154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R13" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,45 +1874,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B14" t="n">
-        <v>80151</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R14" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1984,7 +1984,7 @@
         <v>127119155</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127119902</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127118223</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127118384</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127120162</v>
+        <v>127119947</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594780</v>
+        <v>594720</v>
       </c>
       <c r="R19" t="n">
-        <v>6985201</v>
+        <v>6985260</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127119947</v>
+        <v>127120162</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594720</v>
+        <v>594780</v>
       </c>
       <c r="R20" t="n">
-        <v>6985260</v>
+        <v>6985201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
         <v>127118859</v>
       </c>
       <c r="B21" t="n">
-        <v>96581</v>
+        <v>96584</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127118321</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127119033</v>
       </c>
       <c r="B23" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>127118617</v>
       </c>
       <c r="B24" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127118187</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127117885</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127118668</v>
       </c>
       <c r="B4" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127117979</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127118450</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127120021</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127117753</v>
       </c>
       <c r="B8" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127117773</v>
       </c>
       <c r="B9" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127119304</v>
+        <v>127120216</v>
       </c>
       <c r="B10" t="n">
-        <v>80126</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,34 +1487,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594796</v>
+        <v>594780</v>
       </c>
       <c r="R10" t="n">
-        <v>6985272</v>
+        <v>6985191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127120216</v>
+        <v>127119304</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>80132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,39 +1594,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594780</v>
+        <v>594796</v>
       </c>
       <c r="R11" t="n">
-        <v>6985191</v>
+        <v>6985272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119084</v>
+        <v>127119169</v>
       </c>
       <c r="B12" t="n">
-        <v>91341</v>
+        <v>80160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594836</v>
+        <v>594800</v>
       </c>
       <c r="R12" t="n">
-        <v>6985204</v>
+        <v>6985218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,45 +1777,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B13" t="n">
-        <v>80154</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R13" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,39 +1895,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R14" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1955,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1984,7 +1984,7 @@
         <v>127119155</v>
       </c>
       <c r="B15" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127119902</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127118223</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127118384</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>127119947</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127120162</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>127118859</v>
       </c>
       <c r="B21" t="n">
-        <v>96584</v>
+        <v>96592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127118321</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127119033</v>
       </c>
       <c r="B23" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>127118617</v>
       </c>
       <c r="B24" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -1680,45 +1680,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119169</v>
+        <v>127118286</v>
       </c>
       <c r="B12" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594800</v>
+        <v>594818</v>
       </c>
       <c r="R12" t="n">
-        <v>6985218</v>
+        <v>6985155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,50 +1787,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127118286</v>
+        <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594818</v>
+        <v>594800</v>
       </c>
       <c r="R13" t="n">
-        <v>6985155</v>
+        <v>6985218</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127118187</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R3" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R4" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
         <v>127117979</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127118450</v>
+        <v>127120021</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,34 +1089,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594888</v>
+        <v>594741</v>
       </c>
       <c r="R6" t="n">
-        <v>6985235</v>
+        <v>6985230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1154,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127120021</v>
+        <v>127118450</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,39 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594741</v>
+        <v>594888</v>
       </c>
       <c r="R7" t="n">
-        <v>6985230</v>
+        <v>6985235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,7 +1285,7 @@
         <v>127117753</v>
       </c>
       <c r="B8" t="n">
-        <v>80161</v>
+        <v>80143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127117773</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127120216</v>
+        <v>127119304</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,39 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594780</v>
+        <v>594796</v>
       </c>
       <c r="R10" t="n">
-        <v>6985191</v>
+        <v>6985272</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127119304</v>
+        <v>127120216</v>
       </c>
       <c r="B11" t="n">
-        <v>80132</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,34 +1584,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594796</v>
+        <v>594780</v>
       </c>
       <c r="R11" t="n">
-        <v>6985272</v>
+        <v>6985191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1649,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>91319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,39 +1691,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R12" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,7 +1780,7 @@
         <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>80160</v>
+        <v>80142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127119084</v>
+        <v>127118286</v>
       </c>
       <c r="B14" t="n">
-        <v>91349</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,34 +1885,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594836</v>
+        <v>594818</v>
       </c>
       <c r="R14" t="n">
-        <v>6985204</v>
+        <v>6985155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1984,7 +1984,7 @@
         <v>127119155</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127119902</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127118223</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127118384</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>127119947</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127120162</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>127118859</v>
       </c>
       <c r="B21" t="n">
-        <v>96592</v>
+        <v>96562</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127118321</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127119033</v>
       </c>
       <c r="B23" t="n">
-        <v>80036</v>
+        <v>80018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>127118617</v>
       </c>
       <c r="B24" t="n">
-        <v>80160</v>
+        <v>80142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127118187</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B3" t="n">
-        <v>78770</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R3" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127117885</v>
+        <v>127118668</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>78788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594708</v>
+        <v>594783</v>
       </c>
       <c r="R4" t="n">
-        <v>6985336</v>
+        <v>6985413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
         <v>127117979</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127120021</v>
+        <v>127118450</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,39 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594741</v>
+        <v>594888</v>
       </c>
       <c r="R6" t="n">
-        <v>6985230</v>
+        <v>6985235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127118450</v>
+        <v>127120021</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1186,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594888</v>
+        <v>594741</v>
       </c>
       <c r="R7" t="n">
-        <v>6985235</v>
+        <v>6985230</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1251,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,7 +1285,7 @@
         <v>127117753</v>
       </c>
       <c r="B8" t="n">
-        <v>80143</v>
+        <v>80161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127117773</v>
       </c>
       <c r="B9" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127119304</v>
+        <v>127120216</v>
       </c>
       <c r="B10" t="n">
-        <v>80114</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,34 +1487,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594796</v>
+        <v>594780</v>
       </c>
       <c r="R10" t="n">
-        <v>6985272</v>
+        <v>6985191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127120216</v>
+        <v>127119304</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>80132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,39 +1594,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594780</v>
+        <v>594796</v>
       </c>
       <c r="R11" t="n">
-        <v>6985191</v>
+        <v>6985272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127119084</v>
+        <v>127118286</v>
       </c>
       <c r="B12" t="n">
-        <v>91319</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,34 +1691,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594836</v>
+        <v>594818</v>
       </c>
       <c r="R12" t="n">
-        <v>6985204</v>
+        <v>6985155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1780,7 +1790,7 @@
         <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>80142</v>
+        <v>80160</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127118286</v>
+        <v>127119084</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>91349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,39 +1895,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594818</v>
+        <v>594836</v>
       </c>
       <c r="R14" t="n">
-        <v>6985155</v>
+        <v>6985204</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1955,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1984,7 +1984,7 @@
         <v>127119155</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127119902</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127118223</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127118384</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>127119947</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127120162</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>127118859</v>
       </c>
       <c r="B21" t="n">
-        <v>96562</v>
+        <v>96592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127118321</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127119033</v>
       </c>
       <c r="B23" t="n">
-        <v>80018</v>
+        <v>80036</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>127118617</v>
       </c>
       <c r="B24" t="n">
-        <v>80142</v>
+        <v>80160</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127118187</v>
+        <v>127119084</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594793</v>
+        <v>594836</v>
       </c>
       <c r="R2" t="n">
-        <v>6985170</v>
+        <v>6985204</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127117885</v>
+        <v>127118859</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594708</v>
+        <v>594804</v>
       </c>
       <c r="R3" t="n">
-        <v>6985336</v>
+        <v>6985317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127118668</v>
+        <v>127117885</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594783</v>
+        <v>594708</v>
       </c>
       <c r="R4" t="n">
-        <v>6985413</v>
+        <v>6985336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127117979</v>
+        <v>127118450</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594763</v>
+        <v>594888</v>
       </c>
       <c r="R5" t="n">
-        <v>6985301</v>
+        <v>6985235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127118450</v>
+        <v>127119033</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594888</v>
+        <v>594843</v>
       </c>
       <c r="R6" t="n">
-        <v>6985235</v>
+        <v>6985229</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127120021</v>
+        <v>127117773</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,39 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594741</v>
+        <v>594676</v>
       </c>
       <c r="R7" t="n">
-        <v>6985230</v>
+        <v>6985338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,45 +1257,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127117753</v>
+        <v>127117979</v>
       </c>
       <c r="B8" t="n">
-        <v>80161</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594676</v>
+        <v>594763</v>
       </c>
       <c r="R8" t="n">
-        <v>6985338</v>
+        <v>6985301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127117773</v>
+        <v>127118498</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594676</v>
+        <v>594882</v>
       </c>
       <c r="R9" t="n">
-        <v>6985338</v>
+        <v>6985319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127120216</v>
+        <v>127119155</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,39 +1467,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594780</v>
+        <v>594800</v>
       </c>
       <c r="R10" t="n">
-        <v>6985191</v>
+        <v>6985218</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1527,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,7 +1556,7 @@
         <v>127119304</v>
       </c>
       <c r="B11" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,50 +1650,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127118286</v>
+        <v>127118617</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>80460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594818</v>
+        <v>594797</v>
       </c>
       <c r="R12" t="n">
-        <v>6985155</v>
+        <v>6985417</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1721,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,7 +1750,7 @@
         <v>127119169</v>
       </c>
       <c r="B13" t="n">
-        <v>80160</v>
+        <v>80460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127119084</v>
+        <v>127117753</v>
       </c>
       <c r="B14" t="n">
-        <v>91349</v>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594836</v>
+        <v>594676</v>
       </c>
       <c r="R14" t="n">
-        <v>6985204</v>
+        <v>6985338</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127119155</v>
+        <v>127118187</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1992,34 +1952,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594800</v>
+        <v>594793</v>
       </c>
       <c r="R15" t="n">
-        <v>6985218</v>
+        <v>6985170</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,6 +2017,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127119902</v>
+        <v>127118223</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2118,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594713</v>
+        <v>594803</v>
       </c>
       <c r="R16" t="n">
-        <v>6985271</v>
+        <v>6985163</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127118223</v>
+        <v>127118286</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594803</v>
+        <v>594818</v>
       </c>
       <c r="R17" t="n">
-        <v>6985163</v>
+        <v>6985155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,10 +2262,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127118384</v>
+        <v>127118321</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594843</v>
+        <v>594828</v>
       </c>
       <c r="R18" t="n">
-        <v>6985186</v>
+        <v>6985146</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,10 +2369,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127119947</v>
+        <v>127118384</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594720</v>
+        <v>594843</v>
       </c>
       <c r="R19" t="n">
-        <v>6985260</v>
+        <v>6985186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127120162</v>
+        <v>127119902</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594780</v>
+        <v>594713</v>
       </c>
       <c r="R20" t="n">
-        <v>6985201</v>
+        <v>6985271</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,45 +2583,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127118859</v>
+        <v>127119947</v>
       </c>
       <c r="B21" t="n">
-        <v>96592</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594804</v>
+        <v>594720</v>
       </c>
       <c r="R21" t="n">
-        <v>6985317</v>
+        <v>6985260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,6 +2659,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127118321</v>
+        <v>127120021</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594828</v>
+        <v>594741</v>
       </c>
       <c r="R22" t="n">
-        <v>6985146</v>
+        <v>6985230</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,45 +2797,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127119033</v>
+        <v>127120162</v>
       </c>
       <c r="B23" t="n">
-        <v>80036</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594843</v>
+        <v>594780</v>
       </c>
       <c r="R23" t="n">
-        <v>6985229</v>
+        <v>6985201</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2888,6 +2873,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2914,45 +2904,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127118617</v>
+        <v>127120216</v>
       </c>
       <c r="B24" t="n">
-        <v>80160</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594797</v>
+        <v>594780</v>
       </c>
       <c r="R24" t="n">
-        <v>6985417</v>
+        <v>6985191</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2987,6 +2982,11 @@
           <t>2025-08-03</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3008,6 +3008,103 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127118668</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Halsabäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>594783</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6985413</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24735-2025 artfynd.xlsx
+++ b/artfynd/A 24735-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127119084</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127118859</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127117885</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127118450</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127119033</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127117773</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127117979</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127118498</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127119155</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127119304</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127118617</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127119169</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127117753</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127118187</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127118223</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127118286</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127118321</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2473,6 +2563,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127118384</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2580,6 +2675,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127119902</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2687,6 +2787,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127119947</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2794,6 +2899,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127120021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2901,6 +3011,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127120162</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3008,6 +3123,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127120216</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3105,8 +3225,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127118668</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>